--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,6 +1418,761 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128345224</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91375</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>463631</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6718587</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128345124</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>463614</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6718349</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128345096</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>463618</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6718384</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128345166</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>463636</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6718624</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128345200</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91375</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>463632</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6718603</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128345063</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>463614</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6718417</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128345210</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91375</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster Kroktjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>463633</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6718596</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1960,46 +1960,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128345063</v>
+        <v>128345210</v>
       </c>
       <c r="B14" t="n">
-        <v>98473</v>
+        <v>91375</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463614</v>
+        <v>463633</v>
       </c>
       <c r="R14" t="n">
-        <v>6718417</v>
+        <v>6718596</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2070,41 +2065,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128345210</v>
+        <v>128345063</v>
       </c>
       <c r="B15" t="n">
-        <v>91375</v>
+        <v>98473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463633</v>
+        <v>463614</v>
       </c>
       <c r="R15" t="n">
-        <v>6718596</v>
+        <v>6718417</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1960,41 +1960,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128345210</v>
+        <v>128345063</v>
       </c>
       <c r="B14" t="n">
-        <v>91375</v>
+        <v>98473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2002,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463633</v>
+        <v>463614</v>
       </c>
       <c r="R14" t="n">
-        <v>6718596</v>
+        <v>6718417</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2065,46 +2070,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128345063</v>
+        <v>128345210</v>
       </c>
       <c r="B15" t="n">
-        <v>98473</v>
+        <v>91375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463614</v>
+        <v>463633</v>
       </c>
       <c r="R15" t="n">
-        <v>6718417</v>
+        <v>6718596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1423,7 +1423,7 @@
         <v>128345224</v>
       </c>
       <c r="B9" t="n">
-        <v>91375</v>
+        <v>91380</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128345124</v>
       </c>
       <c r="B10" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>128345096</v>
       </c>
       <c r="B11" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128345166</v>
       </c>
       <c r="B12" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>128345200</v>
       </c>
       <c r="B13" t="n">
-        <v>91375</v>
+        <v>91380</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,46 +1960,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128345063</v>
+        <v>128345210</v>
       </c>
       <c r="B14" t="n">
-        <v>98473</v>
+        <v>91380</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463614</v>
+        <v>463633</v>
       </c>
       <c r="R14" t="n">
-        <v>6718417</v>
+        <v>6718596</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2070,41 +2065,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128345210</v>
+        <v>128345063</v>
       </c>
       <c r="B15" t="n">
-        <v>91375</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463633</v>
+        <v>463614</v>
       </c>
       <c r="R15" t="n">
-        <v>6718596</v>
+        <v>6718417</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1423,7 +1423,7 @@
         <v>128345224</v>
       </c>
       <c r="B9" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128345124</v>
       </c>
       <c r="B10" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>128345096</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128345166</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>128345200</v>
       </c>
       <c r="B13" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128345210</v>
       </c>
       <c r="B14" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128345063</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1423,7 +1423,7 @@
         <v>128345224</v>
       </c>
       <c r="B9" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128345124</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>128345096</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128345166</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>128345200</v>
       </c>
       <c r="B13" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128345210</v>
       </c>
       <c r="B14" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128345063</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1423,7 +1423,7 @@
         <v>128345224</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128345124</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>128345096</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128345166</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>128345200</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128345210</v>
       </c>
       <c r="B14" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128345063</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>128345124</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>128345096</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128345166</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,41 +1960,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128345210</v>
+        <v>128345063</v>
       </c>
       <c r="B14" t="n">
-        <v>91486</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2002,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463633</v>
+        <v>463614</v>
       </c>
       <c r="R14" t="n">
-        <v>6718596</v>
+        <v>6718417</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2065,46 +2070,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128345063</v>
+        <v>128345210</v>
       </c>
       <c r="B15" t="n">
-        <v>98588</v>
+        <v>91486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463614</v>
+        <v>463633</v>
       </c>
       <c r="R15" t="n">
-        <v>6718417</v>
+        <v>6718596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1960,46 +1960,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128345063</v>
+        <v>128345210</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>91486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463614</v>
+        <v>463633</v>
       </c>
       <c r="R14" t="n">
-        <v>6718417</v>
+        <v>6718596</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2070,41 +2065,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128345210</v>
+        <v>128345063</v>
       </c>
       <c r="B15" t="n">
-        <v>91486</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463633</v>
+        <v>463614</v>
       </c>
       <c r="R15" t="n">
-        <v>6718596</v>
+        <v>6718417</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1423,7 +1423,7 @@
         <v>128345224</v>
       </c>
       <c r="B9" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128345124</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>128345096</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128345166</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>128345200</v>
       </c>
       <c r="B13" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,41 +1960,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128345210</v>
+        <v>128345063</v>
       </c>
       <c r="B14" t="n">
-        <v>91486</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2002,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463633</v>
+        <v>463614</v>
       </c>
       <c r="R14" t="n">
-        <v>6718596</v>
+        <v>6718417</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2065,46 +2070,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128345063</v>
+        <v>128345210</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>91487</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463614</v>
+        <v>463633</v>
       </c>
       <c r="R15" t="n">
-        <v>6718417</v>
+        <v>6718596</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1960,46 +1960,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128345063</v>
+        <v>128345210</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>91487</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463614</v>
+        <v>463633</v>
       </c>
       <c r="R14" t="n">
-        <v>6718417</v>
+        <v>6718596</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2070,41 +2065,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128345210</v>
+        <v>128345063</v>
       </c>
       <c r="B15" t="n">
-        <v>91487</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463633</v>
+        <v>463614</v>
       </c>
       <c r="R15" t="n">
-        <v>6718596</v>
+        <v>6718417</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 38390-2025 artfynd.xlsx
+++ b/artfynd/A 38390-2025 artfynd.xlsx
@@ -1423,7 +1423,7 @@
         <v>128345224</v>
       </c>
       <c r="B9" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>128345124</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>128345096</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128345166</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>128345200</v>
       </c>
       <c r="B13" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128345210</v>
       </c>
       <c r="B14" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>128345063</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
